--- a/public/data/productos.xlsx
+++ b/public/data/productos.xlsx
@@ -58,13 +58,13 @@
     <t xml:space="preserve">3 bizcochos de chocolate de 14 cm, 2 rellenos de crema oreo más confituras y drip de chocolate. Rinde de 6 a 8 porciones.</t>
   </si>
   <si>
-    <t xml:space="preserve">Torta Flores</t>
+    <t xml:space="preserve">Torta Panda</t>
   </si>
   <si>
     <t xml:space="preserve">tortas3.avif</t>
   </si>
   <si>
-    <t xml:space="preserve">3 bizcochos de vainilla de 14 cm, 2 rellenos de dulce de leche con cobertura de ganache de chocolate y forrado en fondat. Rinde de 6 a 8 porciones.</t>
+    <t xml:space="preserve">2 bizcochos de vainilla de 14 cm y 1 relleno de ganache de limón. Rinde de 4 a 6 porciones.</t>
   </si>
   <si>
     <t xml:space="preserve">Torta Azzurra</t>
@@ -163,16 +163,16 @@
     <t xml:space="preserve">tortas15.avif</t>
   </si>
   <si>
-    <t xml:space="preserve">3 bizcochos de manteca de 14 cm, 2 rellenos de ganache de almendras y cubierta con buttercream de merengue suizo. Rinde de 6 a 8 porciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torta Osita</t>
+    <t xml:space="preserve">3 bizcochos de manteca de 14 cm, 2 rellenos de ganache de almendras. Rinde de 6 a 8 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta Osito</t>
   </si>
   <si>
     <t xml:space="preserve">tortas11.avif</t>
   </si>
   <si>
-    <t xml:space="preserve">3 bizcochos de chocolate de 14 cm, 2 rellenos de crema Bariloche con cobertura de ganache de chocolate, forrado en fondat y decoración en porcelana fría. Rinde de 6 a 8 porciones.</t>
+    <t xml:space="preserve">2 bizcochos de vainilla de 18 cm, 1 relleno de ganache de limón. Rinde de 8 a 10 porciones.</t>
   </si>
   <si>
     <t xml:space="preserve">Torta Dulce de leche</t>
@@ -551,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -602,7 +602,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
@@ -619,7 +619,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
@@ -636,7 +636,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>22</v>
@@ -653,7 +653,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -670,7 +670,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>28</v>
@@ -687,7 +687,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -704,7 +704,7 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7200</v>
+        <v>6400</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>34</v>
@@ -721,7 +721,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>37</v>
@@ -738,7 +738,7 @@
         <v>39</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>4100</v>
+        <v>3100</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>40</v>
@@ -755,7 +755,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>5700</v>
+        <v>4900</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>43</v>
@@ -767,12 +767,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>3000</v>
+        <v>1900</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>46</v>
@@ -784,12 +784,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>5300</v>
+        <v>2100</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>49</v>
@@ -806,7 +806,7 @@
         <v>51</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>52</v>
@@ -823,7 +823,7 @@
         <v>54</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>3200</v>
+        <v>2900</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>55</v>
@@ -840,7 +840,7 @@
         <v>57</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>58</v>

--- a/public/data/productos.xlsx
+++ b/public/data/productos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
   <si>
     <t xml:space="preserve">Nombre</t>
   </si>
@@ -200,6 +200,51 @@
   </si>
   <si>
     <t xml:space="preserve">2 bizcochos de vainilla de 20 cm, 1 relleno de crema con duraznos más decoración frutal. Rinde de 12 a 15 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta Pingüinos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tortas19.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 bizcochos de vainilla de 14 cm, 2 rellenos de crema de dulce de leche. Rinde de 8 a 12 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta Fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tortas20.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 bizcochos de vainilla de 18 cm, 2 rellenos de crema de coco. Rinde de 15 a 20 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta Choco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tortas21.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 bizcochos de chocolate de 18 cm y 1 relleno de dulce de leche y cubierto de crema bariloche. Rinde de 8 a 10 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta Otoño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tortas22.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 bizcochos de vainilla de 14 cm, 3 rellenos de crema coco. Rinde de 8 a 12 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta Mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tortas23.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 bizcochos de vainilla de 14 cm, 1 relleno de crema de dulce de leche. Rinde de 4 a 6 porciones.</t>
   </si>
   <si>
     <t xml:space="preserve">Pelotita</t>
@@ -314,7 +359,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -335,6 +380,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,7 +430,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -394,6 +445,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -519,7 +574,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.04"/>
@@ -853,119 +908,119 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>35</v>
+        <v>1900</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>82</v>
@@ -976,13 +1031,13 @@
         <v>83</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>85</v>
@@ -993,13 +1048,13 @@
         <v>86</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>88</v>
@@ -1010,13 +1065,13 @@
         <v>89</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>91</v>
@@ -1027,16 +1082,101 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/productos.xlsx
+++ b/public/data/productos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t xml:space="preserve">Nombre</t>
   </si>
@@ -247,109 +247,55 @@
     <t xml:space="preserve">2 bizcochos de vainilla de 14 cm, 1 relleno de crema de dulce de leche. Rinde de 4 a 6 porciones.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelotita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regalo4.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regalos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelotita de goma multicolor, flexible y resistente, perfecta para juegos, piñatas y souvenirs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Globos dorados x10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotillon3.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cotillon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pack de 10 globos dorados de 12", perfectos para decorar fiestas, cumpleaños y eventos especiales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vela dorada c/ número</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotillon2.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vela dorada con número, perfecta para decorar tortas de cumpleaños y celebrar cualquier edad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Globos dorados x20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotillon1.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pack de 20 globos dorados de 12", perfectos para decorar fiestas, cumpleaños y eventos especiales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloques construcción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regalo5.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set de bloques de construcción de más de 15 piezas, ideal para crear, jugar y desarrollar la creatividad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cubo mágico 5 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regalo6.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cubo mágico de colores, perfecto para ejercitar la mente y disfrutar de un desafío entretenido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burbujeros Labubu x3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regalo8.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 burbujeros con diseño tipo Labubu, perfecto para cumpleaños, cotillón, piñatas y diversión al aire libre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burbujeros astro x3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regalo9.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 burbujeros con diseño tipo astronauta, perfecto para cumpleaños, cotillón, piñatas y diversión al aire libre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burbujeros conejito x3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regalo7.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 burbujeros con diseño tipo conejito, perfecto para cumpleaños, cotillón, piñatas y diversión al aire libre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platos desechables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotillon4.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 platos desechables que son resistentes e ideales para servir porciones de torta de forma práctica e higiénica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vasos desechables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotillon5.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 vasos desechables resistentes, ideales para bebidas en fiestas y celebraciones.</t>
+    <t xml:space="preserve">Cake pops x 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesadulce1.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MesaDulce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bizcocho suave, baño de chocolate y decoración a mano. Se venden por docena. Ideales para regalos y eventos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muffins x 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesadulce2.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esponjosos, húmedos y recién horneados. Se venden por docena. Ideales para el desayuno, la merienda y regalos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paletas x 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesadulce3.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate de calidad en su palito, con decoración a mano. Se venden por docena. Ideales para regalos y eventos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promo 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">promos1.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta personalizada de 10 porciones + 12 postres de su elección</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promo 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">promos2.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torta personalizada de 20 porciones + 12 postres de su elección</t>
   </si>
 </sst>
 </file>
@@ -574,13 +520,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="106"/>
   </cols>
   <sheetData>
@@ -997,7 +943,7 @@
         <v>75</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>35</v>
+        <v>900</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>76</v>
@@ -1014,49 +960,49 @@
         <v>79</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1065,118 +1011,16 @@
         <v>89</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>60</v>
+        <v>3200</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/productos.xlsx
+++ b/public/data/productos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="95">
   <si>
     <t xml:space="preserve">Nombre</t>
   </si>
@@ -247,13 +247,22 @@
     <t xml:space="preserve">2 bizcochos de vainilla de 14 cm, 1 relleno de crema de dulce de leche. Rinde de 4 a 6 porciones.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cheesecake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesadulce4.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MesaDulce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliciosa tarta de queso, cremosa y suave, con una base crujiente de galletas y un equilibrio perfecto de dulzura en cada bocado.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cake pops x 12</t>
   </si>
   <si>
     <t xml:space="preserve">mesadulce1.avif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MesaDulce</t>
   </si>
   <si>
     <t xml:space="preserve">Bizcocho suave, baño de chocolate y decoración a mano. Se venden por docena. Ideales para regalos y eventos. </t>
@@ -376,7 +385,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,6 +404,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -520,7 +533,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.04"/>
@@ -939,11 +952,11 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>76</v>
@@ -951,7 +964,7 @@
       <c r="D25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -994,33 +1007,50 @@
         <v>85</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>2400</v>
+        <v>900</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
